--- a/data/trans_orig/P43-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2007</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2007 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621366</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>583427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>656301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>583360</t>
+          <t>583427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>656827</t>
+          <t>656301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,42 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>621366</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>583360</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>656827</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>50,3%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>684576</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>649641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>722515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649115</t>
+          <t>649641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>722582</t>
+          <t>722515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,45 +801,10 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>55,33%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>684576</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>649115</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>722582</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>49,7%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>55,33%</t>
         </is>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305942</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1305942</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1305942</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1305942</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481836</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451438</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>445236</t>
+          <t>451438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>517208</t>
+          <t>522700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>481836</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>445236</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>517208</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>28,19%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1097448</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1056584</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1127846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1062076</t>
+          <t>1056584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1134048</t>
+          <t>1127846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1097448</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1062076</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1134048</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>69,49%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>71,81%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1579284</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1579284</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1579284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1579284</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1579284</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1579284</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170239</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149601</t>
+          <t>151454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192086</t>
+          <t>189904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>170239</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>149601</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>192086</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>40,5%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>284365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324668</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>304030</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>282183</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>324668</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>64,1%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>59,5%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474269</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>474269</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>474269</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>474269</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273441</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1217806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1326804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1215683</t>
+          <t>1217806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1329323</t>
+          <t>1326804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1273441</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1215683</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1329323</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>39,57%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2086053</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2032690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2141688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2030171</t>
+          <t>2032690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2143811</t>
+          <t>2141688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2086053</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2030171</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2143811</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>62,09%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>60,43%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>63,81%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3359494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3359494</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3359494</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3359494</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3359494</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3359494</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2090,13 +1610,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2110,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2129,25 +1648,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2012</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2012 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +1670,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2167,17 +1679,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2248,41 +1749,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2305,13 +1771,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2326,37 +1785,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>796</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>849925</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>810387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>883007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>810559</t>
+          <t>810387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>881897</t>
+          <t>883007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,47 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>849925</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>810559</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>881897</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>63,87%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>60,92%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>66,28%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -2439,37 +1863,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>444</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448733</t>
+          <t>447623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>520071</t>
+          <t>520243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,47 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>480705</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>448733</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>520071</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>36,13%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>33,72%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -2552,37 +1941,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1330630</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1330630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1330630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2616,41 +2005,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1330630</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1330630</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1330630</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2669,37 +2023,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655626</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>699086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>614372</t>
+          <t>611629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>700041</t>
+          <t>699086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,47 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>655626</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>614372</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>700041</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -2782,37 +2101,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1090624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1047164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1134621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1046209</t>
+          <t>1047164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1131878</t>
+          <t>1134621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,47 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1090624</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1046209</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1131878</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>62,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>59,91%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>64,82%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -2895,37 +2179,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1746250</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1746250</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1746250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2959,41 +2243,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1624</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1746250</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1746250</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1746250</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3012,37 +2261,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159533</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137937</t>
+          <t>138455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>184241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,47 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>159533</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>137937</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>184640</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>35,02%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -3125,37 +2339,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>275</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>296067</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270960</t>
+          <t>271359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317663</t>
+          <t>317145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,47 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>296067</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>270960</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>317663</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>64,98%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -3238,37 +2417,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455600</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3302,41 +2481,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>455600</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>455600</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>455600</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3355,37 +2499,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1665084</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1608502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1727307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1600830</t>
+          <t>1608502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1723735</t>
+          <t>1727307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,47 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1665084</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1600830</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1723735</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>45,32%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -3468,37 +2577,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1867395</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1805172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1923977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1808744</t>
+          <t>1805172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1931649</t>
+          <t>1923977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,47 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1867395</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1808744</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1931649</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>52,86%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>51,2%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>54,68%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -3581,37 +2655,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532479</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532479</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3645,41 +2719,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3273</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3532479</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3532479</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3532479</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3693,13 +2732,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3713,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3732,25 +2770,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2016</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +2792,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3770,17 +2801,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3851,41 +2871,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3908,13 +2893,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3929,37 +2907,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>644496</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>675124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>613636</t>
+          <t>611076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>675099</t>
+          <t>675124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,47 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>644496</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>613636</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>675099</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>62,32%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -4042,37 +2985,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340121</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>309493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>373541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309518</t>
+          <t>309493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>370981</t>
+          <t>373541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,47 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>340121</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>309518</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>370981</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>37,68%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3063,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>883</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>984617</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>984617</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>984617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4219,41 +3127,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>883</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>984617</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>984617</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>984617</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4272,37 +3145,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>784</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>857045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>808402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>901229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>814525</t>
+          <t>808402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>906395</t>
+          <t>901229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,47 +3205,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>857045</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>814525</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>906395</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>43,41%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>45,91%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -4385,37 +3223,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1117423</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1073239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1166066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1068073</t>
+          <t>1073239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1159943</t>
+          <t>1166066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,47 +3283,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1117423</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1068073</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1159943</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>56,59%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>54,09%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -4498,37 +3301,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1974468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1974468</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1974468</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4562,41 +3365,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1895</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1974468</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1974468</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1974468</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4615,37 +3383,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248297</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225205</t>
+          <t>224829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274225</t>
+          <t>273846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>248297</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>225205</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>274225</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>45,3%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>50,03%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -4728,37 +3461,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>299867</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273939</t>
+          <t>274318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322959</t>
+          <t>323335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>299867</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>273939</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>322959</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>54,7%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>49,97%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -4841,37 +3539,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548164</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4905,41 +3603,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>548164</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>548164</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>548164</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4958,37 +3621,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1749838</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1691886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1807561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1685137</t>
+          <t>1691886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1807339</t>
+          <t>1807561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,47 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1749838</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1685137</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1807339</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>49,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>48,05%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>51,53%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -5071,37 +3699,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1757411</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1699688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1815363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1699910</t>
+          <t>1699688</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1822112</t>
+          <t>1815363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,47 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1757411</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1699910</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1822112</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>50,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>48,47%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>51,95%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -5184,37 +3777,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3507249</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3507249</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3507249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5248,41 +3841,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3507249</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3507249</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3507249</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5296,13 +3854,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -5316,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5335,25 +3892,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2023</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2023 (tasa de respuesta: 99,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +3914,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5373,17 +3923,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5454,41 +3993,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5511,13 +4015,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5532,37 +4029,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>792</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397625</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +4074,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>379482</t>
+          <t>378477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>417195</t>
+          <t>418315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,47 +4089,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>397625</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>379482</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>417195</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>64,98%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -5645,37 +4107,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214265</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +4152,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194695</t>
+          <t>193575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232408</t>
+          <t>233413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,47 +4167,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>214265</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>194695</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>232408</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>35,02%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -5758,37 +4185,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611890</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611890</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5822,41 +4249,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>611890</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>611890</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>611890</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5875,37 +4267,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>914307</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>778691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1188643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +4312,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>767849</t>
+          <t>778691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1210561</t>
+          <t>1188643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,47 +4327,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>914307</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>767849</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1210561</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>52,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>69,15%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -5988,37 +4345,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>951</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>836267</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>561931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +4390,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540013</t>
+          <t>561931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>982725</t>
+          <t>971883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,47 +4405,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>836267</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>540013</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>982725</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>47,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>56,14%</t>
+          <t>55,52%</t>
         </is>
       </c>
     </row>
@@ -6101,37 +4423,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1750574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1750574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1750574</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6165,41 +4487,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2149</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1750574</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1750574</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1750574</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6218,37 +4505,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267934</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +4550,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248326</t>
+          <t>248867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285854</t>
+          <t>287653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,47 +4565,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>267934</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>248326</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>285854</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>57,95%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>53,71%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>61,83%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -6331,37 +4583,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>194399</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +4628,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176479</t>
+          <t>174680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214007</t>
+          <t>213466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,47 +4643,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>194399</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>176479</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>214007</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>38,17%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>46,29%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -6444,37 +4661,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>462333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>462333</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>462333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6508,41 +4725,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>462333</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>462333</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>462333</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6561,37 +4743,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1579865</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1447681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1859675</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +4788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1444605</t>
+          <t>1447681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1885539</t>
+          <t>1859675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,47 +4803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2461</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1579865</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1444605</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1885539</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>51,14%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>66,75%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -6674,37 +4821,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1244932</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1377116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +4866,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>939258</t>
+          <t>965122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1380192</t>
+          <t>1377116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,47 +4881,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1244932</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>939258</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1380192</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>44,07%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>48,86%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -6787,37 +4899,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2824797</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2824797</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2824797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6851,41 +4963,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2824797</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2824797</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2824797</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6899,13 +4976,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>583427</t>
+          <t>586579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>656301</t>
+          <t>657514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>583427</t>
+          <t>586579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>656301</t>
+          <t>657514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649641</t>
+          <t>648428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>722515</t>
+          <t>719363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649641</t>
+          <t>648428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>722515</t>
+          <t>719363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>451438</t>
+          <t>445471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>522700</t>
+          <t>514822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>451438</t>
+          <t>445471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>522700</t>
+          <t>514822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1056584</t>
+          <t>1064462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1127846</t>
+          <t>1133813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1056584</t>
+          <t>1064462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1127846</t>
+          <t>1133813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151454</t>
+          <t>149839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189904</t>
+          <t>190436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151454</t>
+          <t>149839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189904</t>
+          <t>190436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284365</t>
+          <t>283833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>324430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284365</t>
+          <t>283833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>324430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>810387</t>
+          <t>812285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>883007</t>
+          <t>887018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>810387</t>
+          <t>812285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>883007</t>
+          <t>887018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447623</t>
+          <t>443612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>520243</t>
+          <t>518345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447623</t>
+          <t>443612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>520243</t>
+          <t>518345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>611629</t>
+          <t>617809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>699086</t>
+          <t>695045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>611629</t>
+          <t>617809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>699086</t>
+          <t>695045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1047164</t>
+          <t>1051205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1134621</t>
+          <t>1128441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1047164</t>
+          <t>1051205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1134621</t>
+          <t>1128441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138455</t>
+          <t>138137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>180128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138455</t>
+          <t>138137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>180128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271359</t>
+          <t>275472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317145</t>
+          <t>317463</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271359</t>
+          <t>275472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317145</t>
+          <t>317463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,68%</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1608502</t>
+          <t>1599576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1727307</t>
+          <t>1727552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1608502</t>
+          <t>1599576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1727307</t>
+          <t>1727552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1805172</t>
+          <t>1804927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1923977</t>
+          <t>1932903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1805172</t>
+          <t>1804927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1923977</t>
+          <t>1932903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>611076</t>
+          <t>607365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>675124</t>
+          <t>670793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>611076</t>
+          <t>607365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>675124</t>
+          <t>670793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309493</t>
+          <t>313824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373541</t>
+          <t>377252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309493</t>
+          <t>313824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373541</t>
+          <t>377252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>808402</t>
+          <t>815521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>901229</t>
+          <t>904625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>808402</t>
+          <t>815521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>901229</t>
+          <t>904625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1073239</t>
+          <t>1069843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166066</t>
+          <t>1158947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1073239</t>
+          <t>1069843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1166066</t>
+          <t>1158947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>224829</t>
+          <t>224434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>273846</t>
+          <t>274169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224829</t>
+          <t>224434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>273846</t>
+          <t>274169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274318</t>
+          <t>273995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323335</t>
+          <t>323730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274318</t>
+          <t>273995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323335</t>
+          <t>323730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1691886</t>
+          <t>1690301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1807561</t>
+          <t>1815252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1691886</t>
+          <t>1690301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1807561</t>
+          <t>1815252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1699688</t>
+          <t>1691997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1815363</t>
+          <t>1816948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1699688</t>
+          <t>1691997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1815363</t>
+          <t>1816948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -4034,32 +4034,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>378477</t>
+          <t>409412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>418315</t>
+          <t>450254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4069,32 +4069,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>378477</t>
+          <t>409412</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>418315</t>
+          <t>450254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -4112,32 +4112,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>214265</t>
+          <t>235085</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193575</t>
+          <t>215817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233413</t>
+          <t>256659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>214265</t>
+          <t>235085</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193575</t>
+          <t>215817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233413</t>
+          <t>256659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -4190,17 +4190,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611890</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611890</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611890</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>611890</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>611890</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>611890</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,32 +4272,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>914307</t>
+          <t>732910</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>778691</t>
+          <t>696334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1188643</t>
+          <t>768639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4307,32 +4307,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>914307</t>
+          <t>732910</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>778691</t>
+          <t>696334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1188643</t>
+          <t>768639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>836267</t>
+          <t>887048</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561931</t>
+          <t>851319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>971883</t>
+          <t>923624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>836267</t>
+          <t>887048</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561931</t>
+          <t>851319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>971883</t>
+          <t>923624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1750574</t>
+          <t>1619958</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1750574</t>
+          <t>1619958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1750574</t>
+          <t>1619958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1750574</t>
+          <t>1619958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1750574</t>
+          <t>1619958</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1750574</t>
+          <t>1619958</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248867</t>
+          <t>278173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>287653</t>
+          <t>319376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4545,32 +4545,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248867</t>
+          <t>278173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>287653</t>
+          <t>319376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,35%</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>194399</t>
+          <t>213134</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174680</t>
+          <t>192865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>213466</t>
+          <t>234068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>194399</t>
+          <t>213134</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174680</t>
+          <t>192865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213466</t>
+          <t>234068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4666,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>512241</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>512241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>512241</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>512241</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>512241</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>512241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4748,32 +4748,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1579865</t>
+          <t>1463003</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1447681</t>
+          <t>1416926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1859675</t>
+          <t>1506547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4783,32 +4783,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1579865</t>
+          <t>1463003</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1447681</t>
+          <t>1416926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1859675</t>
+          <t>1506547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -4826,32 +4826,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1244932</t>
+          <t>1335268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>965122</t>
+          <t>1291724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1377116</t>
+          <t>1381345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,32 +4861,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1244932</t>
+          <t>1335268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>965122</t>
+          <t>1291724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1377116</t>
+          <t>1381345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4904,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2824797</t>
+          <t>2798271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2824797</t>
+          <t>2798271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2824797</t>
+          <t>2798271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2824797</t>
+          <t>2798271</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2824797</t>
+          <t>2798271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2824797</t>
+          <t>2798271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
